--- a/uat-test-plans-reduced30/G2-16314-migrate-registered-user-data-from-wcs-to-tapir.xlsx
+++ b/uat-test-plans-reduced30/G2-16314-migrate-registered-user-data-from-wcs-to-tapir.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[Reduced ~22% — 7/9 checks retained, lowest-priority sections dropped] 4 UI-testable migration stories mapped to 9 business checks and 7 coverage rows. 9 non-UI stories and spikes are excluded from direct business execution.</t>
+          <t>[Reduced V2 ~22% — 7/9 checks retained; AC and core-case coverage guardrails enforced] 4 UI-testable migration stories mapped to 9 business checks and 7 coverage rows. 9 non-UI stories and spikes are excluded from direct business execution.</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>payload_bytes=11585; payload_chars=11583; est_tokens~2896; checklist_rows=7; matrix_rows=7; exploratory_rows=3</t>
+          <t>payload_bytes=11597; payload_chars=11595; est_tokens~2899; checklist_rows=7; matrix_rows=7; exploratory_rows=3</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
@@ -941,7 +941,7 @@
     <row r="7" ht="64" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>UAT-006</t>
+          <t>UAT-007</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -951,23 +951,23 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Non-auth Feature Reuse</t>
+          <t>Idempotency Outcome</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Migrated customer data is usable in non-auth account features</t>
+          <t>Reprocessed migrated account set does not create visible duplicates</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>After login, navigate account sections that rely on migrated customer attributes and verify pages render without missing-customer-state errors.</t>
+          <t>Use post-rerun sample accounts agreed with operations and re-check profile/address pages for duplicate account identity or duplicated address entities.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Account pages depending on migrated profile data render correctly.
-No user-facing data integrity errors are shown.</t>
+          <t>No duplicate account identity is visible.
+No duplicate address entities are introduced by reprocessing.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr"/>
@@ -976,7 +976,7 @@
     <row r="8" ht="64" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>UAT-007</t>
+          <t>UAT-008</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -986,23 +986,23 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Idempotency Outcome</t>
+          <t>Cross-brand Consistency</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Reprocessed migrated account set does not create visible duplicates</t>
+          <t>Migration outcomes are consistent across both acceptance storefronts</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Use post-rerun sample accounts agreed with operations and re-check profile/address pages for duplicate account identity or duplicated address entities.</t>
+          <t>Execute key checks on both target URLs with equivalent migrated-user samples and compare behavior.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>No duplicate account identity is visible.
-No duplicate address entities are introduced by reprocessing.</t>
+          <t>Critical migration outcomes are consistent across both environments.
+No brand-specific blocker is found for account or address continuity.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>UAT-002, UAT-006</t>
+          <t>UAT-002</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>UAT-003</t>
+          <t>UAT-003, UAT-008</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>UAT-001</t>
+          <t>UAT-001, UAT-008</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">

--- a/uat-test-plans-reduced30/G2-16314-migrate-registered-user-data-from-wcs-to-tapir.xlsx
+++ b/uat-test-plans-reduced30/G2-16314-migrate-registered-user-data-from-wcs-to-tapir.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[Reduced V2 ~22% — 7/9 checks retained; AC and core-case coverage guardrails enforced] 4 UI-testable migration stories mapped to 9 business checks and 7 coverage rows. 9 non-UI stories and spikes are excluded from direct business execution.</t>
+          <t>[Reduced V2 ~22% — 7/9 checks retained; AC coverage guardrail enforced] 4 UI-testable migration stories mapped to 9 business checks and 7 coverage rows. 9 non-UI stories and spikes are excluded from direct business execution.</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>payload_bytes=11597; payload_chars=11595; est_tokens~2899; checklist_rows=7; matrix_rows=7; exploratory_rows=3</t>
+          <t>payload_bytes=11582; payload_chars=11580; est_tokens~2895; checklist_rows=7; matrix_rows=7; exploratory_rows=3</t>
         </is>
       </c>
     </row>
